--- a/ibu_schedule.xlsx
+++ b/ibu_schedule.xlsx
@@ -1,60 +1,60 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Config" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PWDs" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Employees" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Availability" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule_2026_06_15" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule_2026_06_08" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule_2026_06_01" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule_2026_05_25" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule_2026_05_18" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule_2026_05_11" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule_2026_05_04" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule_2026_04_27" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule_2026_04_20" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule_2026_04_13" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule_2026_04_06" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule_2026_03_30" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule_2026_03_23" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule_2026_03_16" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule_2026_03_09" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule_2026_03_02" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule_2026_02_23" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule_2026_02_16" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule_2026_02_09" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule_2026_02_02" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule_2026_01_26" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule_2025_01_19" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule_2025_01_12" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule_2025_01_05" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule_2025_12_29" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule_2025_12_22" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule_2025_12_15" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule_2025_12_08" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule_2025_12_01" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule_2025_11_24" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule_2025_11_17" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule_2025_11_10" sheetId="36" state="visible" r:id="rId36"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule_2025_11_03" sheetId="37" state="visible" r:id="rId37"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule_2025_10_27" sheetId="38" state="visible" r:id="rId38"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule_2025_10_20" sheetId="39" state="visible" r:id="rId39"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule_2025_10_13" sheetId="40" state="visible" r:id="rId40"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule_2025_10_06" sheetId="41" state="visible" r:id="rId41"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule_2025_09_29" sheetId="42" state="visible" r:id="rId42"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule_2025_09_22" sheetId="43" state="visible" r:id="rId43"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule_2025_09_15" sheetId="44" state="visible" r:id="rId44"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule_2025_09_08" sheetId="45" state="visible" r:id="rId45"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule_2025_09_01" sheetId="46" state="visible" r:id="rId46"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule_2025_08_25" sheetId="47" state="visible" r:id="rId47"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule_2025_08_18" sheetId="48" state="visible" r:id="rId48"/>
+    <sheet name="Config" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="PWDs" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Employees" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Availability" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Schedule_2026_06_15" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Schedule_2026_06_08" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Schedule_2026_06_01" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Schedule_2026_05_25" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Schedule_2026_05_18" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Schedule_2026_05_11" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Schedule_2026_05_04" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Schedule_2026_04_27" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Schedule_2026_04_20" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Schedule_2026_04_13" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Schedule_2026_04_06" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Schedule_2026_03_30" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Schedule_2026_03_23" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Schedule_2026_03_16" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Schedule_2026_03_09" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Schedule_2026_03_02" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Schedule_2026_02_23" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Schedule_2026_02_16" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Schedule_2026_02_09" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Schedule_2026_02_02" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Schedule_2026_01_26" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="Schedule_2025_01_19" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="Schedule_2025_01_12" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="Schedule_2025_01_05" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="Schedule_2025_12_29" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="Schedule_2025_12_22" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="Schedule_2025_12_15" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="Schedule_2025_12_08" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="Schedule_2025_12_01" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="Schedule_2025_11_24" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="Schedule_2025_11_17" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="Schedule_2025_11_10" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet name="Schedule_2025_11_03" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet name="Schedule_2025_10_27" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet name="Schedule_2025_10_20" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet name="Schedule_2025_10_13" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet name="Schedule_2025_10_06" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet name="Schedule_2025_09_29" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet name="Schedule_2025_09_22" sheetId="43" state="visible" r:id="rId43"/>
+    <sheet name="Schedule_2025_09_15" sheetId="44" state="visible" r:id="rId44"/>
+    <sheet name="Schedule_2025_09_08" sheetId="45" state="visible" r:id="rId45"/>
+    <sheet name="Schedule_2025_09_01" sheetId="46" state="visible" r:id="rId46"/>
+    <sheet name="Schedule_2025_08_25" sheetId="47" state="visible" r:id="rId47"/>
+    <sheet name="Schedule_2025_08_18" sheetId="48" state="visible" r:id="rId48"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -503,7 +503,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
@@ -587,7 +587,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N36"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -2449,7 +2449,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -4000,7 +4000,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -5495,7 +5495,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N34"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -7270,7 +7270,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N37"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -9173,7 +9173,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -10316,7 +10316,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -11326,7 +11326,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -12122,7 +12122,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -13163,7 +13163,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -14398,7 +14398,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
@@ -14447,7 +14447,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>888281da8992ec02</t>
+          <t>240be518fabd2724</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-06-14T17:27:37.788767</t>
+          <t>2026-06-15T01:00:31.453627</t>
         </is>
       </c>
     </row>
@@ -14473,7 +14473,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -15519,7 +15519,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -16361,7 +16361,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -17111,7 +17111,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -17897,7 +17897,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -19173,7 +19173,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -20107,7 +20107,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -21092,7 +21092,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -21745,7 +21745,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -22531,7 +22531,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -23639,7 +23639,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
@@ -23705,7 +23705,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -24900,7 +24900,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N35"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -26611,7 +26611,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N39"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -28531,7 +28531,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N36"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -30293,7 +30293,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -31519,7 +31519,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -32556,7 +32556,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -33266,7 +33266,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N41"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -35283,7 +35283,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -36641,7 +36641,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N34"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -38296,7 +38296,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:P1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -38410,7 +38410,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N40"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -40351,7 +40351,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N33"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -41955,7 +41955,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -43288,7 +43288,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -44504,7 +44504,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -45715,7 +45715,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -46972,7 +46972,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -47998,7 +47998,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -49485,7 +49485,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -50517,7 +50517,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -51308,7 +51308,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -52650,7 +52650,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N40"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -54691,7 +54691,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N51"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -57303,7 +57303,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>

--- a/ibu_schedule.xlsx
+++ b/ibu_schedule.xlsx
@@ -51307,7 +51307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N26"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -52637,6 +52637,53 @@
           <t>Event</t>
         </is>
       </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>shift_1781485261990</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>emp_001</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>monday</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>ground_floor</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>7</v>
+      </c>
+      <c r="J27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L27" t="b">
+        <v>0</v>
+      </c>
+      <c r="N27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/ibu_schedule.xlsx
+++ b/ibu_schedule.xlsx
@@ -52661,7 +52661,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -52675,7 +52675,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J27" t="b">
         <v>0</v>

--- a/ibu_schedule.xlsx
+++ b/ibu_schedule.xlsx
@@ -52661,7 +52661,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -52675,7 +52675,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J27" t="b">
         <v>0</v>

--- a/ibu_schedule.xlsx
+++ b/ibu_schedule.xlsx
@@ -15922,8 +15922,8 @@
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="D31:J31"/>
+    <mergeCell ref="D32:J32"/>
     <mergeCell ref="D28:J28"/>
-    <mergeCell ref="D32:J32"/>
     <mergeCell ref="D30:J30"/>
     <mergeCell ref="D24:J24"/>
     <mergeCell ref="D29:J29"/>
@@ -17284,8 +17284,8 @@
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="D31:J31"/>
+    <mergeCell ref="D32:J32"/>
     <mergeCell ref="D28:J28"/>
-    <mergeCell ref="D32:J32"/>
     <mergeCell ref="D30:J30"/>
     <mergeCell ref="D24:J24"/>
     <mergeCell ref="D29:J29"/>
@@ -18630,8 +18630,8 @@
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="D31:J31"/>
+    <mergeCell ref="D32:J32"/>
     <mergeCell ref="D28:J28"/>
-    <mergeCell ref="D32:J32"/>
     <mergeCell ref="D30:J30"/>
     <mergeCell ref="D24:J24"/>
     <mergeCell ref="D29:J29"/>
@@ -21607,8 +21607,8 @@
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="D31:J31"/>
+    <mergeCell ref="D32:J32"/>
     <mergeCell ref="D28:J28"/>
-    <mergeCell ref="D32:J32"/>
     <mergeCell ref="D30:J30"/>
     <mergeCell ref="D24:J24"/>
     <mergeCell ref="D29:J29"/>
@@ -28306,8 +28306,8 @@
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="D31:J31"/>
+    <mergeCell ref="D32:J32"/>
     <mergeCell ref="D28:J28"/>
-    <mergeCell ref="D32:J32"/>
     <mergeCell ref="D30:J30"/>
     <mergeCell ref="D24:J24"/>
     <mergeCell ref="D29:J29"/>
@@ -29519,7 +29519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD33"/>
+  <dimension ref="A1:Q33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.45"/>
   <cols>
     <col width="26.28515625" customWidth="1" min="1" max="1"/>
@@ -35028,7 +35028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S33"/>
+  <dimension ref="A1:Q33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.45"/>
   <cols>
     <col width="26.28515625" customWidth="1" min="1" max="1"/>
@@ -52837,7 +52837,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>b22ce7fd18070390</t>
+          <t>240be518fabd2724</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -52847,7 +52847,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-06-15T13:03:49.624452</t>
+          <t>2026-06-15T13:40:52.268943</t>
         </is>
       </c>
     </row>
